--- a/xls/square_12_tri3_6.xlsx
+++ b/xls/square_12_tri3_6.xlsx
@@ -418,7 +418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CAF0E20E-E4D8-9B45-9C94-E89B574F109C}">
-  <dimension ref="A1:K16"/>
+  <dimension ref="A1:K32"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:11">
@@ -482,13 +482,13 @@
         <v>216</v>
       </c>
       <c r="I6">
-        <v>5.031023074169107</v>
+        <v>5.031024001761756</v>
       </c>
       <c r="J6">
-        <v>1.886421775126925</v>
+        <v>1.8864232017566647</v>
       </c>
       <c r="K6">
-        <v>1.785869986863326</v>
+        <v>1.7858708346735497</v>
       </c>
     </row>
     <row r="7" spans="1:11">
@@ -517,13 +517,13 @@
         <v>294</v>
       </c>
       <c r="I7">
-        <v>-1.4009568113708808</v>
+        <v>-1.4009569249463316</v>
       </c>
       <c r="J7">
-        <v>-1.294340622951219</v>
+        <v>-1.2943404665880816</v>
       </c>
       <c r="K7">
-        <v>-0.7905927943603783</v>
+        <v>-0.7905928277598439</v>
       </c>
     </row>
     <row r="8" spans="1:11">
@@ -552,13 +552,13 @@
         <v>384</v>
       </c>
       <c r="I8">
-        <v>-1.409118329339053</v>
+        <v>-1.4091182909146835</v>
       </c>
       <c r="J8">
-        <v>-1.4215125960141368</v>
+        <v>-1.4215125639626218</v>
       </c>
       <c r="K8">
-        <v>-0.7822190686036313</v>
+        <v>-0.7822190408590237</v>
       </c>
     </row>
     <row r="9" spans="1:11">
@@ -587,13 +587,13 @@
         <v>486</v>
       </c>
       <c r="I9">
-        <v>-1.136565789973653</v>
+        <v>-1.1365658185971186</v>
       </c>
       <c r="J9">
-        <v>-0.8507420534602644</v>
+        <v>-0.8507420500367135</v>
       </c>
       <c r="K9">
-        <v>-0.14016705526170892</v>
+        <v>-0.14016706984299027</v>
       </c>
     </row>
     <row r="10" spans="1:11">
@@ -622,13 +622,13 @@
         <v>600</v>
       </c>
       <c r="I10">
-        <v>-1.3980803638601063</v>
+        <v>-1.3980801022676261</v>
       </c>
       <c r="J10">
-        <v>-1.2489359530995816</v>
+        <v>-1.2489358961218613</v>
       </c>
       <c r="K10">
-        <v>-0.46113215375947475</v>
+        <v>-0.46113212892564237</v>
       </c>
     </row>
     <row r="11" spans="1:11">
@@ -657,13 +657,13 @@
         <v>726</v>
       </c>
       <c r="I11">
-        <v>-0.4309613592498462</v>
+        <v>-0.4309613740601409</v>
       </c>
       <c r="J11">
-        <v>-0.4172559913701247</v>
+        <v>-0.4172560065815893</v>
       </c>
       <c r="K11">
-        <v>0.33144707555872915</v>
+        <v>0.33144706893416126</v>
       </c>
     </row>
     <row r="12" spans="1:11">
@@ -692,13 +692,13 @@
         <v>864</v>
       </c>
       <c r="I12">
-        <v>-0.7355167546718768</v>
+        <v>-0.73551675983214</v>
       </c>
       <c r="J12">
-        <v>-0.6934715073749417</v>
+        <v>-0.6934715152750944</v>
       </c>
       <c r="K12">
-        <v>0.10632466099343835</v>
+        <v>0.10632465916796748</v>
       </c>
     </row>
     <row r="13" spans="1:11">
@@ -727,13 +727,13 @@
         <v>1014</v>
       </c>
       <c r="I13">
-        <v>0.0038620302242534923</v>
+        <v>0.0038620306227842047</v>
       </c>
       <c r="J13">
-        <v>-0.0027095295115055432</v>
+        <v>-0.0027095295628996843</v>
       </c>
       <c r="K13">
-        <v>2.643917926277827</v>
+        <v>2.643917942010636</v>
       </c>
     </row>
     <row r="14" spans="1:11">
@@ -762,13 +762,13 @@
         <v>1176</v>
       </c>
       <c r="I14">
-        <v>-0.00018616902568128013</v>
+        <v>-0.0001861690256925676</v>
       </c>
       <c r="J14">
-        <v>-0.000181703802692786</v>
+        <v>-0.00018170380269664493</v>
       </c>
       <c r="K14">
-        <v>2.5609174003745285</v>
+        <v>2.560917400359842</v>
       </c>
     </row>
     <row r="15" spans="1:11">
@@ -797,13 +797,13 @@
         <v>1350</v>
       </c>
       <c r="I15">
-        <v>-4.299574441520713e-5</v>
+        <v>-4.29957444206079e-5</v>
       </c>
       <c r="J15">
-        <v>-3.612495841360442e-5</v>
+        <v>-3.612495841620832e-5</v>
       </c>
       <c r="K15">
-        <v>2.1705311330535912</v>
+        <v>2.170531132616653</v>
       </c>
     </row>
     <row r="16" spans="1:11">
@@ -832,13 +832,573 @@
         <v>1536</v>
       </c>
       <c r="I16">
-        <v>2.496832277547654e-6</v>
+        <v>2.496832277644086e-6</v>
       </c>
       <c r="J16">
-        <v>-2.068831597701139e-6</v>
+        <v>-2.068831597797572e-6</v>
       </c>
       <c r="K16">
-        <v>1.8275607423099327</v>
+        <v>1.8275607421281324</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>11</v>
+      </c>
+      <c r="B17">
+        <v>49</v>
+      </c>
+      <c r="C17" t="s">
+        <v>11</v>
+      </c>
+      <c r="D17">
+        <v>169</v>
+      </c>
+      <c r="E17" t="s">
+        <v>12</v>
+      </c>
+      <c r="F17">
+        <v>324</v>
+      </c>
+      <c r="G17" t="s">
+        <v>13</v>
+      </c>
+      <c r="H17">
+        <v>1734</v>
+      </c>
+      <c r="I17">
+        <v>3.1514570752541286e-6</v>
+      </c>
+      <c r="J17">
+        <v>3.871933816075872e-8</v>
+      </c>
+      <c r="K17">
+        <v>1.6803086889904604</v>
+      </c>
+    </row>
+    <row r="18" spans="1:11">
+      <c r="A18" t="s">
+        <v>11</v>
+      </c>
+      <c r="B18">
+        <v>49</v>
+      </c>
+      <c r="C18" t="s">
+        <v>11</v>
+      </c>
+      <c r="D18">
+        <v>169</v>
+      </c>
+      <c r="E18" t="s">
+        <v>12</v>
+      </c>
+      <c r="F18">
+        <v>361</v>
+      </c>
+      <c r="G18" t="s">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1944</v>
+      </c>
+      <c r="I18">
+        <v>3.1241958546313275e-7</v>
+      </c>
+      <c r="J18">
+        <v>-1.9677000196794757e-7</v>
+      </c>
+      <c r="K18">
+        <v>1.404594775688159</v>
+      </c>
+    </row>
+    <row r="19" spans="1:11">
+      <c r="A19" t="s">
+        <v>11</v>
+      </c>
+      <c r="B19">
+        <v>49</v>
+      </c>
+      <c r="C19" t="s">
+        <v>11</v>
+      </c>
+      <c r="D19">
+        <v>169</v>
+      </c>
+      <c r="E19" t="s">
+        <v>12</v>
+      </c>
+      <c r="F19">
+        <v>400</v>
+      </c>
+      <c r="G19" t="s">
+        <v>13</v>
+      </c>
+      <c r="H19">
+        <v>2166</v>
+      </c>
+      <c r="I19">
+        <v>-4.577269954363227e-8</v>
+      </c>
+      <c r="J19">
+        <v>-5.238091283859189e-8</v>
+      </c>
+      <c r="K19">
+        <v>0.8421887676192829</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>11</v>
+      </c>
+      <c r="B20">
+        <v>49</v>
+      </c>
+      <c r="C20" t="s">
+        <v>11</v>
+      </c>
+      <c r="D20">
+        <v>169</v>
+      </c>
+      <c r="E20" t="s">
+        <v>12</v>
+      </c>
+      <c r="F20">
+        <v>441</v>
+      </c>
+      <c r="G20" t="s">
+        <v>13</v>
+      </c>
+      <c r="H20">
+        <v>2400</v>
+      </c>
+      <c r="I20">
+        <v>-6.048331698861083e-8</v>
+      </c>
+      <c r="J20">
+        <v>-5.87831098898978e-8</v>
+      </c>
+      <c r="K20">
+        <v>0.8283617957895492</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>11</v>
+      </c>
+      <c r="B21">
+        <v>49</v>
+      </c>
+      <c r="C21" t="s">
+        <v>11</v>
+      </c>
+      <c r="D21">
+        <v>169</v>
+      </c>
+      <c r="E21" t="s">
+        <v>12</v>
+      </c>
+      <c r="F21">
+        <v>484</v>
+      </c>
+      <c r="G21" t="s">
+        <v>13</v>
+      </c>
+      <c r="H21">
+        <v>2646</v>
+      </c>
+      <c r="I21">
+        <v>-5.677537805341615e-8</v>
+      </c>
+      <c r="J21">
+        <v>-5.357609147818945e-8</v>
+      </c>
+      <c r="K21">
+        <v>0.8041099279327566</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>11</v>
+      </c>
+      <c r="B22">
+        <v>49</v>
+      </c>
+      <c r="C22" t="s">
+        <v>11</v>
+      </c>
+      <c r="D22">
+        <v>169</v>
+      </c>
+      <c r="E22" t="s">
+        <v>12</v>
+      </c>
+      <c r="F22">
+        <v>529</v>
+      </c>
+      <c r="G22" t="s">
+        <v>13</v>
+      </c>
+      <c r="H22">
+        <v>2904</v>
+      </c>
+      <c r="I22">
+        <v>-5.6788642861616636e-8</v>
+      </c>
+      <c r="J22">
+        <v>-5.4613249423676315e-8</v>
+      </c>
+      <c r="K22">
+        <v>0.8114945731529</v>
+      </c>
+    </row>
+    <row r="23" spans="1:11">
+      <c r="A23" t="s">
+        <v>11</v>
+      </c>
+      <c r="B23">
+        <v>49</v>
+      </c>
+      <c r="C23" t="s">
+        <v>11</v>
+      </c>
+      <c r="D23">
+        <v>169</v>
+      </c>
+      <c r="E23" t="s">
+        <v>12</v>
+      </c>
+      <c r="F23">
+        <v>576</v>
+      </c>
+      <c r="G23" t="s">
+        <v>13</v>
+      </c>
+      <c r="H23">
+        <v>3174</v>
+      </c>
+      <c r="I23">
+        <v>-5.1608296665738134e-8</v>
+      </c>
+      <c r="J23">
+        <v>-5.0700836254461766e-8</v>
+      </c>
+      <c r="K23">
+        <v>0.8024888802351585</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11">
+      <c r="A24" t="s">
+        <v>11</v>
+      </c>
+      <c r="B24">
+        <v>49</v>
+      </c>
+      <c r="C24" t="s">
+        <v>11</v>
+      </c>
+      <c r="D24">
+        <v>169</v>
+      </c>
+      <c r="E24" t="s">
+        <v>12</v>
+      </c>
+      <c r="F24">
+        <v>625</v>
+      </c>
+      <c r="G24" t="s">
+        <v>13</v>
+      </c>
+      <c r="H24">
+        <v>3456</v>
+      </c>
+      <c r="I24">
+        <v>-5.531846276781752e-8</v>
+      </c>
+      <c r="J24">
+        <v>-5.3405379844472875e-8</v>
+      </c>
+      <c r="K24">
+        <v>0.8086750500457992</v>
+      </c>
+    </row>
+    <row r="25" spans="1:11">
+      <c r="A25" t="s">
+        <v>11</v>
+      </c>
+      <c r="B25">
+        <v>49</v>
+      </c>
+      <c r="C25" t="s">
+        <v>11</v>
+      </c>
+      <c r="D25">
+        <v>169</v>
+      </c>
+      <c r="E25" t="s">
+        <v>12</v>
+      </c>
+      <c r="F25">
+        <v>676</v>
+      </c>
+      <c r="G25" t="s">
+        <v>13</v>
+      </c>
+      <c r="H25">
+        <v>3750</v>
+      </c>
+      <c r="I25">
+        <v>-5.1615870783858803e-8</v>
+      </c>
+      <c r="J25">
+        <v>-5.005477525359443e-8</v>
+      </c>
+      <c r="K25">
+        <v>0.7963058077019628</v>
+      </c>
+    </row>
+    <row r="26" spans="1:11">
+      <c r="A26" t="s">
+        <v>11</v>
+      </c>
+      <c r="B26">
+        <v>49</v>
+      </c>
+      <c r="C26" t="s">
+        <v>11</v>
+      </c>
+      <c r="D26">
+        <v>169</v>
+      </c>
+      <c r="E26" t="s">
+        <v>12</v>
+      </c>
+      <c r="F26">
+        <v>729</v>
+      </c>
+      <c r="G26" t="s">
+        <v>13</v>
+      </c>
+      <c r="H26">
+        <v>4056</v>
+      </c>
+      <c r="I26">
+        <v>-5.424078763274956e-8</v>
+      </c>
+      <c r="J26">
+        <v>-5.16693570685022e-8</v>
+      </c>
+      <c r="K26">
+        <v>0.7978394647033304</v>
+      </c>
+    </row>
+    <row r="27" spans="1:11">
+      <c r="A27" t="s">
+        <v>11</v>
+      </c>
+      <c r="B27">
+        <v>49</v>
+      </c>
+      <c r="C27" t="s">
+        <v>11</v>
+      </c>
+      <c r="D27">
+        <v>169</v>
+      </c>
+      <c r="E27" t="s">
+        <v>12</v>
+      </c>
+      <c r="F27">
+        <v>784</v>
+      </c>
+      <c r="G27" t="s">
+        <v>13</v>
+      </c>
+      <c r="H27">
+        <v>4374</v>
+      </c>
+      <c r="I27">
+        <v>-5.310589952336183e-8</v>
+      </c>
+      <c r="J27">
+        <v>-5.034820287412318e-8</v>
+      </c>
+      <c r="K27">
+        <v>0.7915482279092868</v>
+      </c>
+    </row>
+    <row r="28" spans="1:11">
+      <c r="A28" t="s">
+        <v>11</v>
+      </c>
+      <c r="B28">
+        <v>49</v>
+      </c>
+      <c r="C28" t="s">
+        <v>11</v>
+      </c>
+      <c r="D28">
+        <v>169</v>
+      </c>
+      <c r="E28" t="s">
+        <v>12</v>
+      </c>
+      <c r="F28">
+        <v>841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>13</v>
+      </c>
+      <c r="H28">
+        <v>4704</v>
+      </c>
+      <c r="I28">
+        <v>-5.3034042798059974e-8</v>
+      </c>
+      <c r="J28">
+        <v>-5.052104581523618e-8</v>
+      </c>
+      <c r="K28">
+        <v>0.7930912620300555</v>
+      </c>
+    </row>
+    <row r="29" spans="1:11">
+      <c r="A29" t="s">
+        <v>11</v>
+      </c>
+      <c r="B29">
+        <v>49</v>
+      </c>
+      <c r="C29" t="s">
+        <v>11</v>
+      </c>
+      <c r="D29">
+        <v>169</v>
+      </c>
+      <c r="E29" t="s">
+        <v>12</v>
+      </c>
+      <c r="F29">
+        <v>900</v>
+      </c>
+      <c r="G29" t="s">
+        <v>13</v>
+      </c>
+      <c r="H29">
+        <v>5046</v>
+      </c>
+      <c r="I29">
+        <v>-5.18697025845546e-8</v>
+      </c>
+      <c r="J29">
+        <v>-4.9686733703107634e-8</v>
+      </c>
+      <c r="K29">
+        <v>0.7914391609330936</v>
+      </c>
+    </row>
+    <row r="30" spans="1:11">
+      <c r="A30" t="s">
+        <v>11</v>
+      </c>
+      <c r="B30">
+        <v>49</v>
+      </c>
+      <c r="C30" t="s">
+        <v>11</v>
+      </c>
+      <c r="D30">
+        <v>169</v>
+      </c>
+      <c r="E30" t="s">
+        <v>12</v>
+      </c>
+      <c r="F30">
+        <v>961</v>
+      </c>
+      <c r="G30" t="s">
+        <v>13</v>
+      </c>
+      <c r="H30">
+        <v>5400</v>
+      </c>
+      <c r="I30">
+        <v>-5.2854360025043224e-8</v>
+      </c>
+      <c r="J30">
+        <v>-5.045944813752315e-8</v>
+      </c>
+      <c r="K30">
+        <v>0.7936909959122999</v>
+      </c>
+    </row>
+    <row r="31" spans="1:11">
+      <c r="A31" t="s">
+        <v>11</v>
+      </c>
+      <c r="B31">
+        <v>49</v>
+      </c>
+      <c r="C31" t="s">
+        <v>11</v>
+      </c>
+      <c r="D31">
+        <v>169</v>
+      </c>
+      <c r="E31" t="s">
+        <v>12</v>
+      </c>
+      <c r="F31">
+        <v>1024</v>
+      </c>
+      <c r="G31" t="s">
+        <v>13</v>
+      </c>
+      <c r="H31">
+        <v>5766</v>
+      </c>
+      <c r="I31">
+        <v>-5.1833050807560895e-8</v>
+      </c>
+      <c r="J31">
+        <v>-4.951647747461788e-8</v>
+      </c>
+      <c r="K31">
+        <v>0.7899249975022768</v>
+      </c>
+    </row>
+    <row r="32" spans="1:11">
+      <c r="A32" t="s">
+        <v>11</v>
+      </c>
+      <c r="B32">
+        <v>49</v>
+      </c>
+      <c r="C32" t="s">
+        <v>11</v>
+      </c>
+      <c r="D32">
+        <v>169</v>
+      </c>
+      <c r="E32" t="s">
+        <v>12</v>
+      </c>
+      <c r="F32">
+        <v>1089</v>
+      </c>
+      <c r="G32" t="s">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>6144</v>
+      </c>
+      <c r="I32">
+        <v>-5.2436680384876186e-8</v>
+      </c>
+      <c r="J32">
+        <v>-4.987356329935461e-8</v>
+      </c>
+      <c r="K32">
+        <v>0.7901194590494014</v>
       </c>
     </row>
   </sheetData>
